--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138EE822-71DC-4352-BE44-D281D8426BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46807889-7309-4DA1-9141-9D4EF97F064C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
   <si>
     <t>location</t>
   </si>
@@ -281,6 +281,15 @@
   </si>
   <si>
     <t>AQ</t>
+  </si>
+  <si>
+    <t>Umrechnung notwendig?</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
+    <t>nein</t>
   </si>
 </sst>
 </file>
@@ -296,7 +305,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,8 +336,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -466,11 +481,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -494,6 +548,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1011,17 +1071,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E32"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.5703125" customWidth="1"/>
     <col min="3" max="3" width="39.42578125" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
         <v>29</v>
@@ -1032,8 +1093,11 @@
       <c r="E3" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1046,8 +1110,11 @@
       <c r="E4" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1060,8 +1127,11 @@
       <c r="E5" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
@@ -1074,8 +1144,11 @@
       <c r="E6" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1161,11 @@
       <c r="E7" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1102,8 +1178,11 @@
       <c r="E8" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
@@ -1116,8 +1195,11 @@
       <c r="E9" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1130,8 +1212,11 @@
       <c r="E10" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1144,8 +1229,11 @@
       <c r="E11" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1158,8 +1246,11 @@
       <c r="E12" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1172,8 +1263,11 @@
       <c r="E13" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1186,8 +1280,11 @@
       <c r="E14" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>11</v>
       </c>
@@ -1200,8 +1297,11 @@
       <c r="E15" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
@@ -1214,8 +1314,11 @@
       <c r="E16" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
@@ -1228,8 +1331,11 @@
       <c r="E17" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1348,11 @@
       <c r="E18" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,8 +1365,11 @@
       <c r="E19" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
@@ -1270,8 +1382,11 @@
       <c r="E20" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1284,8 +1399,11 @@
       <c r="E21" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
@@ -1298,8 +1416,11 @@
       <c r="E22" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
@@ -1312,8 +1433,11 @@
       <c r="E23" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>20</v>
       </c>
@@ -1326,8 +1450,11 @@
       <c r="E24" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>21</v>
       </c>
@@ -1340,8 +1467,11 @@
       <c r="E25" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
         <v>22</v>
       </c>
@@ -1350,8 +1480,9 @@
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="23"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
@@ -1364,8 +1495,11 @@
       <c r="E27" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>24</v>
       </c>
@@ -1378,8 +1512,11 @@
       <c r="E28" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1529,11 @@
       <c r="E29" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
         <v>26</v>
       </c>
@@ -1402,8 +1542,9 @@
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="16"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="23"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>27</v>
       </c>
@@ -1412,8 +1553,9 @@
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
-    </row>
-    <row r="32" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="20" t="s">
         <v>28</v>
       </c>
@@ -1422,6 +1564,7 @@
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="18"/>
+      <c r="F32" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46807889-7309-4DA1-9141-9D4EF97F064C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C29A26-C98E-47B5-A1DE-A03462FA5B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="88">
   <si>
     <t>location</t>
   </si>
@@ -34,12 +34,6 @@
     <t>well_or_spring_name</t>
   </si>
   <si>
-    <t>utm_e</t>
-  </si>
-  <si>
-    <t>utm_n</t>
-  </si>
-  <si>
     <t>depth_bgl_in_m</t>
   </si>
   <si>
@@ -290,6 +284,12 @@
   </si>
   <si>
     <t>nein</t>
+  </si>
+  <si>
+    <t>WGS84_latitude</t>
+  </si>
+  <si>
+    <t>WGS84_longitude</t>
   </si>
 </sst>
 </file>
@@ -550,7 +550,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
@@ -834,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40B4A1F-305E-4A10-9B22-5AB123015450}">
-  <dimension ref="B2:E32"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -842,224 +842,257 @@
     <col min="3" max="3" width="31.7109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="28.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="6"/>
       <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6"/>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="23"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6"/>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="23"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="C7" s="6"/>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="23"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="6"/>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="23"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" s="6"/>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="23"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" s="6"/>
       <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="23"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6"/>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6"/>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="23"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6"/>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="23"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6"/>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="23"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="23"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6"/>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" s="6"/>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="23"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" s="6"/>
       <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="23"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C20" s="6"/>
       <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="23"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" s="6"/>
       <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="23"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="6"/>
       <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="23"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="6"/>
       <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="23"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6"/>
       <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="23"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25" s="6"/>
       <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="23"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C26" s="6"/>
       <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="23"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C27" s="6"/>
       <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="23"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="6"/>
       <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="23"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" s="6"/>
       <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="23"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C30" s="6"/>
       <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="23"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" s="6"/>
       <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="4"/>
       <c r="E32" s="5"/>
+      <c r="F32" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1085,16 +1118,16 @@
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
@@ -1102,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="F4" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
@@ -1119,364 +1152,364 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>86</v>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>86</v>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F10" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
@@ -1484,61 +1517,61 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="16"/>
@@ -1546,10 +1579,10 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
@@ -1557,10 +1590,10 @@
     </row>
     <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="18"/>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C29A26-C98E-47B5-A1DE-A03462FA5B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CFED53-F39F-468B-90B5-709E5C861814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
-    <sheet name="REFLECT Datenbank" sheetId="1" r:id="rId2"/>
+    <sheet name="USGS" sheetId="5" r:id="rId2"/>
+    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId3"/>
+    <sheet name="CAES2014" sheetId="3" r:id="rId4"/>
+    <sheet name="REFLECT" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="188">
   <si>
     <t>location</t>
   </si>
@@ -290,6 +293,306 @@
   </si>
   <si>
     <t>WGS84_longitude</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>SamplingFeatureName</t>
+  </si>
+  <si>
+    <t>LatDegree</t>
+  </si>
+  <si>
+    <t>LongDegree</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>DrilledDepth_ft</t>
+  </si>
+  <si>
+    <t>ja | von ft in m</t>
+  </si>
+  <si>
+    <t>FluidTemperature_C</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>ph_Field</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>TotalDissolvedSolids_mgL</t>
+  </si>
+  <si>
+    <t>ja | Addition der mmol/L</t>
+  </si>
+  <si>
+    <t>Na_mgL</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Mg_mgL</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>ja | in mmol/L</t>
+  </si>
+  <si>
+    <t>Ca_mgL</t>
+  </si>
+  <si>
+    <t>CX</t>
+  </si>
+  <si>
+    <t>Cl_mgL</t>
+  </si>
+  <si>
+    <t>CY</t>
+  </si>
+  <si>
+    <t>SO4_mgL</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>K_mgL</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>Sr_mgL</t>
+  </si>
+  <si>
+    <t>EB</t>
+  </si>
+  <si>
+    <t>ja | in μmol/L</t>
+  </si>
+  <si>
+    <t>F_mgL</t>
+  </si>
+  <si>
+    <t>CZ</t>
+  </si>
+  <si>
+    <t>Li_mgL</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>Alkalinity_mgL</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>nicht vorhanden - IDAHO eintragen</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Sheet1</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Temperature_C</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Conductivity_uS_cm</t>
+  </si>
+  <si>
+    <t>nicht vorhanden, wird berechnet</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>ja | Addition in mmol/L</t>
+  </si>
+  <si>
+    <t>HCO3_mgL</t>
+  </si>
+  <si>
+    <t>Li_ugL</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Sr_ugL</t>
+  </si>
+  <si>
+    <t>Fe_ugL</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Mn_ugL</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>NO3_mgL</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>COUNTY</t>
+  </si>
+  <si>
+    <t>WELLNAME</t>
+  </si>
+  <si>
+    <t>LATITUDE</t>
+  </si>
+  <si>
+    <t>LONGITUDE</t>
+  </si>
+  <si>
+    <t>PERIOD</t>
+  </si>
+  <si>
+    <t>DEPTHLOWER</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>TEMP</t>
+  </si>
+  <si>
+    <t>nein, wenige Daten</t>
+  </si>
+  <si>
+    <t>LITHOLOGY</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>ja | Addition der mmol/L  | ACHTUNG - ähnliches Attribut TSUSGS</t>
+  </si>
+  <si>
+    <t>HCO3</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja | in mmol/L  </t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>SO4</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>Sr</t>
+  </si>
+  <si>
+    <t>Mn</t>
+  </si>
+  <si>
+    <t>NO3</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>FeTot</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja | in μmol/L  </t>
+  </si>
+  <si>
+    <t>DY</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>DH</t>
   </si>
 </sst>
 </file>
@@ -305,7 +608,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,8 +645,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -520,11 +829,224 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -554,6 +1076,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -958,60 +1515,57 @@
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="23"/>
+      <c r="F16" s="41"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="23"/>
+      <c r="F18" s="41"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="23"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="23"/>
+      <c r="F20" s="41"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="23"/>
+      <c r="F21" s="41"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="23"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="46"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
@@ -1100,6 +1654,1450 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
+  <dimension ref="B2:I32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="59.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="I12" s="61"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="60" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" s="62" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28484C-C581-4663-8490-31B7BD27263E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:F32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="56"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783802C3-70F2-469E-9F15-66886A2B472E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:F32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="29"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="29"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="29"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1352,19 +3350,19 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="45" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1437,19 +3435,19 @@
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F22" s="43" t="s">
         <v>84</v>
       </c>
     </row>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CFED53-F39F-468B-90B5-709E5C861814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09838B02-C711-4762-BB9F-A9CD21780430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="CAES2014" sheetId="3" r:id="rId4"/>
     <sheet name="REFLECT" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="189">
   <si>
     <t>location</t>
   </si>
@@ -593,6 +593,9 @@
   </si>
   <si>
     <t>DH</t>
+  </si>
+  <si>
+    <t>NH4</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1106,9 +1109,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1655,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
-  <dimension ref="B2:I32"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.85546875" customWidth="1"/>
@@ -1665,8 +1665,8 @@
     <col min="6" max="6" width="59.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -1681,7 +1681,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
         <v>6</v>
       </c>
@@ -1827,9 +1827,8 @@
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
       <c r="F12" s="29"/>
-      <c r="I12" s="61"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1846,7 +1845,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1856,7 @@
       <c r="E14" s="16"/>
       <c r="F14" s="29"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
@@ -1874,7 +1873,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
         <v>10</v>
       </c>
@@ -1898,7 +1897,7 @@
       <c r="E17" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="60" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1994,13 +1993,13 @@
       <c r="C23" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="59" t="s">
+      <c r="D23" t="s">
         <v>134</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F23" s="60" t="s">
+      <c r="F23" s="26" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2042,8 +2041,15 @@
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="E26" s="2"/>
+      <c r="C26" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="F26" s="26" t="s">
         <v>181</v>
       </c>
@@ -2140,7 +2146,7 @@
       <c r="E32" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F32" s="62" t="s">
+      <c r="F32" s="59" t="s">
         <v>166</v>
       </c>
     </row>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09838B02-C711-4762-BB9F-A9CD21780430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50595504-BEC3-4E0D-BFEC-5F6ACF63229A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="192">
   <si>
     <t>location</t>
   </si>
@@ -596,6 +596,15 @@
   </si>
   <si>
     <t>NH4</t>
+  </si>
+  <si>
+    <t>Anmerkung</t>
+  </si>
+  <si>
+    <t>liegt falsch in ug/L vor</t>
+  </si>
+  <si>
+    <t>manche Daten in ppm, ausgehen von mg/L = ppm, da Dichte unbekannt</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -654,6 +663,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="35">
     <border>
@@ -1049,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1111,6 +1126,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1391,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40B4A1F-305E-4A10-9B22-5AB123015450}">
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -1400,10 +1419,11 @@
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="28.28515625" customWidth="1"/>
     <col min="6" max="6" width="27.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -1417,111 +1437,127 @@
       <c r="F3" s="25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="6"/>
       <c r="E4" s="2"/>
       <c r="F4" s="23"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6"/>
       <c r="E5" s="2"/>
       <c r="F5" s="23"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6"/>
       <c r="E6" s="2"/>
       <c r="F6" s="23"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6"/>
       <c r="E7" s="2"/>
       <c r="F7" s="23"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="6"/>
       <c r="E8" s="2"/>
       <c r="F8" s="23"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="6"/>
       <c r="E9" s="2"/>
       <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="6"/>
       <c r="E10" s="2"/>
       <c r="F10" s="23"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="6"/>
       <c r="E11" s="2"/>
       <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="6"/>
       <c r="E12" s="2"/>
       <c r="F12" s="23"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6"/>
       <c r="E13" s="2"/>
       <c r="F13" s="23"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6"/>
       <c r="E14" s="2"/>
       <c r="F14" s="23"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6"/>
       <c r="E15" s="2"/>
       <c r="F15" s="23"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6"/>
       <c r="F16" s="41"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
@@ -1529,36 +1565,41 @@
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
       <c r="F17" s="40"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6"/>
       <c r="F18" s="41"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6"/>
       <c r="F19" s="41"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6"/>
       <c r="F20" s="41"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6"/>
       <c r="F21" s="41"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
@@ -1566,80 +1607,90 @@
       <c r="D22" s="36"/>
       <c r="E22" s="37"/>
       <c r="F22" s="46"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="6"/>
       <c r="E23" s="2"/>
       <c r="F23" s="23"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="62"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6"/>
       <c r="E24" s="2"/>
       <c r="F24" s="23"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="63"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="6"/>
       <c r="E25" s="2"/>
       <c r="F25" s="23"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="62"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="6"/>
       <c r="E26" s="2"/>
       <c r="F26" s="23"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="63"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="6"/>
       <c r="E27" s="2"/>
       <c r="F27" s="23"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="62"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="6"/>
       <c r="E28" s="2"/>
       <c r="F28" s="23"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="62"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="6"/>
       <c r="E29" s="2"/>
       <c r="F29" s="23"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="6"/>
       <c r="E30" s="2"/>
       <c r="F30" s="23"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="6"/>
       <c r="E31" s="2"/>
       <c r="F31" s="23"/>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>26</v>
       </c>
@@ -1647,6 +1698,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="5"/>
       <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1655,7 +1707,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
-  <dimension ref="B2:F32"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.85546875" customWidth="1"/>
@@ -1663,10 +1718,11 @@
     <col min="4" max="4" width="25.28515625" customWidth="1"/>
     <col min="5" max="5" width="28.7109375" customWidth="1"/>
     <col min="6" max="6" width="59.85546875" customWidth="1"/>
+    <col min="7" max="7" width="67.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -1680,8 +1736,11 @@
       <c r="F3" s="25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1697,8 +1756,9 @@
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1714,8 +1774,9 @@
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
@@ -1731,8 +1792,9 @@
       <c r="F6" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
@@ -1748,8 +1810,9 @@
       <c r="F7" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
@@ -1765,8 +1828,9 @@
       <c r="F8" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
@@ -1782,8 +1846,9 @@
       <c r="F9" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1799,8 +1864,9 @@
       <c r="F10" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
@@ -1816,8 +1882,9 @@
       <c r="F11" s="28" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
         <v>6</v>
       </c>
@@ -1827,8 +1894,9 @@
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
       <c r="F12" s="29"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1844,8 +1912,9 @@
       <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
@@ -1855,8 +1924,9 @@
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="29"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
@@ -1872,8 +1942,11 @@
       <c r="F15" s="26" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
         <v>10</v>
       </c>
@@ -1883,8 +1956,9 @@
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="48"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
@@ -1900,8 +1974,11 @@
       <c r="F17" s="60" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
@@ -1917,8 +1994,11 @@
       <c r="F18" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
@@ -1934,8 +2014,11 @@
       <c r="F19" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
@@ -1951,8 +2034,11 @@
       <c r="F20" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
@@ -1968,8 +2054,11 @@
       <c r="F21" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
@@ -1985,8 +2074,11 @@
       <c r="F22" s="43" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
@@ -2002,8 +2094,11 @@
       <c r="F23" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2019,8 +2114,11 @@
       <c r="F24" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2036,8 +2134,11 @@
       <c r="F25" s="26" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
@@ -2053,8 +2154,11 @@
       <c r="F26" s="26" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
@@ -2070,8 +2174,11 @@
       <c r="F27" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2087,8 +2194,11 @@
       <c r="F28" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2104,8 +2214,11 @@
       <c r="F29" s="26" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2121,8 +2234,11 @@
       <c r="F30" s="26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>25</v>
       </c>
@@ -2132,8 +2248,9 @@
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
       <c r="F31" s="29"/>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>26</v>
       </c>
@@ -2149,9 +2266,13 @@
       <c r="F32" s="59" t="s">
         <v>166</v>
       </c>
+      <c r="G32" s="64" t="s">
+        <v>191</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="91" scale="38" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2160,7 +2281,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.7109375" customWidth="1"/>
@@ -2168,10 +2289,11 @@
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="28.7109375" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11"/>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2185,8 +2307,11 @@
       <c r="F3" s="25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2202,8 +2327,9 @@
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -2219,8 +2345,9 @@
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
@@ -2236,8 +2363,9 @@
       <c r="F6" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
@@ -2253,8 +2381,9 @@
       <c r="F7" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>2</v>
       </c>
@@ -2264,8 +2393,9 @@
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="29"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="30" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2405,9 @@
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="29"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>4</v>
       </c>
@@ -2286,8 +2417,9 @@
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
       <c r="F10" s="29"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
@@ -2303,8 +2435,9 @@
       <c r="F11" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2320,8 +2453,9 @@
       <c r="F12" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -2337,8 +2471,9 @@
       <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
@@ -2350,8 +2485,9 @@
       <c r="F14" s="26" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="49" t="s">
         <v>9</v>
       </c>
@@ -2361,8 +2497,9 @@
       <c r="D15" s="51"/>
       <c r="E15" s="52"/>
       <c r="F15" s="53"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
         <v>10</v>
       </c>
@@ -2372,8 +2509,9 @@
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="48"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
@@ -2389,8 +2527,9 @@
       <c r="F17" s="45" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
@@ -2406,8 +2545,9 @@
       <c r="F18" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
@@ -2423,8 +2563,9 @@
       <c r="F19" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
@@ -2440,8 +2581,9 @@
       <c r="F20" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
@@ -2457,8 +2599,9 @@
       <c r="F21" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
@@ -2474,8 +2617,9 @@
       <c r="F22" s="43" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
@@ -2491,8 +2635,11 @@
       <c r="F23" s="45" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
@@ -2508,8 +2655,9 @@
       <c r="F24" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2525,8 +2673,11 @@
       <c r="F25" s="26" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
         <v>20</v>
       </c>
@@ -2536,8 +2687,9 @@
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
       <c r="F26" s="29"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
@@ -2553,8 +2705,11 @@
       <c r="F27" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G27" s="61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2570,8 +2725,11 @@
       <c r="F28" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G28" s="61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2587,8 +2745,9 @@
       <c r="F29" s="26" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2604,8 +2763,9 @@
       <c r="F30" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>25</v>
       </c>
@@ -2617,8 +2777,9 @@
       <c r="F31" s="29" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="54" t="s">
         <v>26</v>
       </c>
@@ -2630,10 +2791,11 @@
       <c r="F32" s="58" t="s">
         <v>112</v>
       </c>
+      <c r="G32" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50595504-BEC3-4E0D-BFEC-5F6ACF63229A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3745E880-0F6C-46B5-829B-3D2A81E2C200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
-    <sheet name="USGS" sheetId="5" r:id="rId2"/>
-    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId3"/>
-    <sheet name="CAES2014" sheetId="3" r:id="rId4"/>
-    <sheet name="REFLECT" sheetId="1" r:id="rId5"/>
+    <sheet name="ALPS" sheetId="6" r:id="rId2"/>
+    <sheet name="USGS" sheetId="5" r:id="rId3"/>
+    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId4"/>
+    <sheet name="CAES2014" sheetId="3" r:id="rId5"/>
+    <sheet name="REFLECT" sheetId="1" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913" concurrentCalc="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="218">
   <si>
     <t>location</t>
   </si>
@@ -605,6 +606,84 @@
   </si>
   <si>
     <t>manche Daten in ppm, ausgehen von mg/L = ppm, da Dichte unbekannt</t>
+  </si>
+  <si>
+    <t>CAES2014</t>
+  </si>
+  <si>
+    <t>REFLECT</t>
+  </si>
+  <si>
+    <t>MDPI Tibet</t>
+  </si>
+  <si>
+    <t>USGS</t>
+  </si>
+  <si>
+    <t>ALPS</t>
+  </si>
+  <si>
+    <t>spring location</t>
+  </si>
+  <si>
+    <t>spring name</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>well_depth_(m)</t>
+  </si>
+  <si>
+    <t>Na_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>Ca_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>Mg_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>Cl_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>HCO3_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>SO4_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>Li_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>temperature_(degr_C)</t>
+  </si>
+  <si>
+    <t>EC_(S_m^-1)</t>
+  </si>
+  <si>
+    <t>TDS_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>K_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>NH4_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>F_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>NO3_(mg L^-1)</t>
+  </si>
+  <si>
+    <t>lithology</t>
+  </si>
+  <si>
+    <t>ja | von S/m in uS/cm</t>
   </si>
 </sst>
 </file>
@@ -670,7 +749,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1060,11 +1139,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1126,10 +1216,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1616,7 +1705,7 @@
       <c r="C23" s="6"/>
       <c r="E23" s="2"/>
       <c r="F23" s="23"/>
-      <c r="G23" s="62"/>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
@@ -1625,7 +1714,7 @@
       <c r="C24" s="6"/>
       <c r="E24" s="2"/>
       <c r="F24" s="23"/>
-      <c r="G24" s="63"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
@@ -1634,7 +1723,7 @@
       <c r="C25" s="6"/>
       <c r="E25" s="2"/>
       <c r="F25" s="23"/>
-      <c r="G25" s="62"/>
+      <c r="G25" s="23"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
@@ -1643,7 +1732,7 @@
       <c r="C26" s="6"/>
       <c r="E26" s="2"/>
       <c r="F26" s="23"/>
-      <c r="G26" s="63"/>
+      <c r="G26" s="23"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
@@ -1652,7 +1741,7 @@
       <c r="C27" s="6"/>
       <c r="E27" s="2"/>
       <c r="F27" s="23"/>
-      <c r="G27" s="62"/>
+      <c r="G27" s="23"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
@@ -1661,7 +1750,7 @@
       <c r="C28" s="6"/>
       <c r="E28" s="2"/>
       <c r="F28" s="23"/>
-      <c r="G28" s="62"/>
+      <c r="G28" s="23"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
@@ -1706,6 +1795,416 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6DB8F-FD5C-4693-8887-04E42CDC7E06}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1723,7 +2222,9 @@
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="11"/>
+      <c r="B3" s="11" t="s">
+        <v>195</v>
+      </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
@@ -2266,7 +2767,7 @@
       <c r="F32" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2276,7 +2777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28484C-C581-4663-8490-31B7BD27263E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2294,7 +2795,9 @@
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="11"/>
+      <c r="B3" s="11" t="s">
+        <v>194</v>
+      </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
@@ -2799,7 +3302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783802C3-70F2-469E-9F15-66886A2B472E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2816,7 +3319,9 @@
   <sheetData>
     <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="11"/>
+      <c r="B3" s="11" t="s">
+        <v>192</v>
+      </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
@@ -3265,7 +3770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3282,7 +3787,9 @@
   <sheetData>
     <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="11"/>
+      <c r="B3" s="11" t="s">
+        <v>193</v>
+      </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,29 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3745E880-0F6C-46B5-829B-3D2A81E2C200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1697FD-B7AB-42A5-A17E-92AFC57BFC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
-    <sheet name="ALPS" sheetId="6" r:id="rId2"/>
-    <sheet name="USGS" sheetId="5" r:id="rId3"/>
-    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId4"/>
-    <sheet name="CAES2014" sheetId="3" r:id="rId5"/>
-    <sheet name="REFLECT" sheetId="1" r:id="rId6"/>
+    <sheet name="HESSEN" sheetId="7" r:id="rId2"/>
+    <sheet name="MOESM2" sheetId="8" r:id="rId3"/>
+    <sheet name="ALPS" sheetId="6" r:id="rId4"/>
+    <sheet name="USGS" sheetId="5" r:id="rId5"/>
+    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId6"/>
+    <sheet name="CAES2014" sheetId="3" r:id="rId7"/>
+    <sheet name="REFLECT" sheetId="1" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="271">
   <si>
     <t>location</t>
   </si>
@@ -684,6 +695,165 @@
   </si>
   <si>
     <t>ja | von S/m in uS/cm</t>
+  </si>
+  <si>
+    <t>ja | ist in Zahlen kodiert</t>
+  </si>
+  <si>
+    <t>Town</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Well or Spring Name</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Zeile 3</t>
+  </si>
+  <si>
+    <t>ja | in Long und Lat</t>
+  </si>
+  <si>
+    <t>Coordinates R</t>
+  </si>
+  <si>
+    <t>Coordinates H</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Final depth</t>
+  </si>
+  <si>
+    <t>Rock type</t>
+  </si>
+  <si>
+    <t>Zeile 4</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Electric</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>Zeile 3 + 5 Kombi</t>
+  </si>
+  <si>
+    <t>AH</t>
+  </si>
+  <si>
+    <t>Redox</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Total dissolved solids calculated</t>
+  </si>
+  <si>
+    <t>As</t>
+  </si>
+  <si>
+    <t>Egal, wird später berechnet</t>
+  </si>
+  <si>
+    <t>Sodium</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>Magnesium</t>
+  </si>
+  <si>
+    <t>Calcium</t>
+  </si>
+  <si>
+    <t>Chloride</t>
+  </si>
+  <si>
+    <t>Sulphate</t>
+  </si>
+  <si>
+    <t>Bicarbonate</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>Lithium</t>
+  </si>
+  <si>
+    <t>Potassium</t>
+  </si>
+  <si>
+    <t>Strontium</t>
+  </si>
+  <si>
+    <t>Ammonium</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Manganese</t>
+  </si>
+  <si>
+    <t>Fluoride</t>
+  </si>
+  <si>
+    <t>Nitrate</t>
+  </si>
+  <si>
+    <t>Silica</t>
+  </si>
+  <si>
+    <t>Oxigen</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>BD</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>BJ</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>???????????</t>
+  </si>
+  <si>
+    <t>?????????????</t>
+  </si>
+  <si>
+    <t>Table1</t>
+  </si>
+  <si>
+    <t>MOESM2 (vsl. nicht nutzbar)</t>
+  </si>
+  <si>
+    <t>Hessen (muss angepasst werden)</t>
+  </si>
+  <si>
+    <t>zu wenig Daten</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1219,6 +1389,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1795,6 +1966,966 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A059286-C8A1-4672-9077-497707963BB5}">
+  <dimension ref="B2:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>220</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D20" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D31" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8011DF-EFF6-4FCD-84E2-B9EE254EAD4E}">
+  <dimension ref="B2:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="30.28515625" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6DB8F-FD5C-4693-8887-04E42CDC7E06}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1904,8 +3035,8 @@
         <v>216</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="28" t="s">
-        <v>85</v>
+      <c r="F9" s="26" t="s">
+        <v>218</v>
       </c>
       <c r="G9" s="23"/>
     </row>
@@ -2204,7 +3335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2777,7 +3908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28484C-C581-4663-8490-31B7BD27263E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3302,7 +4433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783802C3-70F2-469E-9F15-66886A2B472E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3770,7 +4901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1697FD-B7AB-42A5-A17E-92AFC57BFC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9EF0BC-B2FB-4984-BFFE-776774711319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
-    <sheet name="HESSEN" sheetId="7" r:id="rId2"/>
-    <sheet name="MOESM2" sheetId="8" r:id="rId3"/>
-    <sheet name="ALPS" sheetId="6" r:id="rId4"/>
-    <sheet name="USGS" sheetId="5" r:id="rId5"/>
-    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId6"/>
-    <sheet name="CAES2014" sheetId="3" r:id="rId7"/>
-    <sheet name="REFLECT" sheetId="1" r:id="rId8"/>
+    <sheet name="|---&gt; nutzbare" sheetId="11" r:id="rId2"/>
+    <sheet name="SVZ_Chile" sheetId="9" r:id="rId3"/>
+    <sheet name="HESSEN" sheetId="7" r:id="rId4"/>
+    <sheet name="ALPS" sheetId="6" r:id="rId5"/>
+    <sheet name="USGS" sheetId="5" r:id="rId6"/>
+    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId7"/>
+    <sheet name="CAES2014" sheetId="3" r:id="rId8"/>
+    <sheet name="REFLECT" sheetId="1" r:id="rId9"/>
+    <sheet name="|---&gt; nicht nutzbare" sheetId="10" r:id="rId10"/>
+    <sheet name="MOESM2" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="290">
   <si>
     <t>location</t>
   </si>
@@ -854,6 +857,63 @@
   </si>
   <si>
     <t>zu wenig Daten</t>
+  </si>
+  <si>
+    <t>Location_name</t>
+  </si>
+  <si>
+    <t>Table1_Merged</t>
+  </si>
+  <si>
+    <t>Fault_domain</t>
+  </si>
+  <si>
+    <t>Ableiten aus Location_name (grob)</t>
+  </si>
+  <si>
+    <t>t_C</t>
+  </si>
+  <si>
+    <t>TDS_ppm</t>
+  </si>
+  <si>
+    <t>Cl_ppm</t>
+  </si>
+  <si>
+    <t>SO4_ppm</t>
+  </si>
+  <si>
+    <t>HCO3_ppm</t>
+  </si>
+  <si>
+    <t>K_ppm</t>
+  </si>
+  <si>
+    <t>Na_ppm</t>
+  </si>
+  <si>
+    <t>Mg_ppm</t>
+  </si>
+  <si>
+    <t>Ca_ppm</t>
+  </si>
+  <si>
+    <t>Li_ppb</t>
+  </si>
+  <si>
+    <t>Sr_ppb</t>
+  </si>
+  <si>
+    <t>Schätzen aus Location_name (grob)</t>
+  </si>
+  <si>
+    <t>liegt in ppb vor, müsste in ppm vorliegen</t>
+  </si>
+  <si>
+    <t>SVZ_Chile</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1390,6 +1450,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1965,7 +2026,819 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAC61E6-50DF-405D-A52F-EDADE72AA266}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8011DF-EFF6-4FCD-84E2-B9EE254EAD4E}">
+  <dimension ref="B2:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="30.28515625" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF34DBC-9B7A-4964-BEA9-A6721237D408}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D46C7FC-4F92-409B-95F3-5697C13BE790}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D20" t="s">
+        <v>272</v>
+      </c>
+      <c r="E20" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" t="s">
+        <v>272</v>
+      </c>
+      <c r="E21" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" t="s">
+        <v>272</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" t="s">
+        <v>272</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" t="s">
+        <v>272</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="31"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A059286-C8A1-4672-9077-497707963BB5}">
   <dimension ref="B2:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2584,348 +3457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8011DF-EFF6-4FCD-84E2-B9EE254EAD4E}">
-  <dimension ref="B2:G32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="37.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="30.28515625" customWidth="1"/>
-    <col min="7" max="7" width="32.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="23"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24" t="s">
-        <v>270</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6DB8F-FD5C-4693-8887-04E42CDC7E06}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3335,7 +3867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3908,7 +4440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28484C-C581-4663-8490-31B7BD27263E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4433,7 +4965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783802C3-70F2-469E-9F15-66886A2B472E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4901,7 +5433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,22 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9EF0BC-B2FB-4984-BFFE-776774711319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FCC783-BE1B-4338-8651-9368BB735F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
-    <sheet name="|---&gt; nutzbare" sheetId="11" r:id="rId2"/>
-    <sheet name="SVZ_Chile" sheetId="9" r:id="rId3"/>
-    <sheet name="HESSEN" sheetId="7" r:id="rId4"/>
-    <sheet name="ALPS" sheetId="6" r:id="rId5"/>
-    <sheet name="USGS" sheetId="5" r:id="rId6"/>
-    <sheet name="MDPI_Tibet" sheetId="4" r:id="rId7"/>
-    <sheet name="CAES2014" sheetId="3" r:id="rId8"/>
-    <sheet name="REFLECT" sheetId="1" r:id="rId9"/>
-    <sheet name="|---&gt; nicht nutzbare" sheetId="10" r:id="rId10"/>
-    <sheet name="MOESM2" sheetId="8" r:id="rId11"/>
+    <sheet name="|-&gt; nutzbar" sheetId="11" r:id="rId2"/>
+    <sheet name="1_MDPI_Tibet" sheetId="4" r:id="rId3"/>
+    <sheet name="2_CAES2014" sheetId="3" r:id="rId4"/>
+    <sheet name="3_REFLECT" sheetId="1" r:id="rId5"/>
+    <sheet name="5_ALPS" sheetId="6" r:id="rId6"/>
+    <sheet name="6_HESSEN" sheetId="7" r:id="rId7"/>
+    <sheet name="7_Yukon" sheetId="18" r:id="rId8"/>
+    <sheet name="8_Southern_Thailand" sheetId="17" r:id="rId9"/>
+    <sheet name="9_Australia" sheetId="14" r:id="rId10"/>
+    <sheet name="10_MPDI_Xianshuihe" sheetId="16" r:id="rId11"/>
+    <sheet name="11_MMC1" sheetId="15" r:id="rId12"/>
+    <sheet name="12_Argonne" sheetId="13" r:id="rId13"/>
+    <sheet name="13_SVZ_Chile" sheetId="9" r:id="rId14"/>
+    <sheet name="|-&gt; vlt." sheetId="12" r:id="rId15"/>
+    <sheet name="4_USGS" sheetId="5" r:id="rId16"/>
+    <sheet name="|-&gt; nicht" sheetId="10" r:id="rId17"/>
+    <sheet name="MOESM2" sheetId="8" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="370">
   <si>
     <t>location</t>
   </si>
@@ -841,12 +848,6 @@
     <t>BM</t>
   </si>
   <si>
-    <t>???????????</t>
-  </si>
-  <si>
-    <t>?????????????</t>
-  </si>
-  <si>
     <t>Table1</t>
   </si>
   <si>
@@ -914,13 +915,259 @@
   </si>
   <si>
     <t>W</t>
+  </si>
+  <si>
+    <t>Yukon</t>
+  </si>
+  <si>
+    <t>Southern_Thailand</t>
+  </si>
+  <si>
+    <t>Xianshuihe</t>
+  </si>
+  <si>
+    <t>MMC1</t>
+  </si>
+  <si>
+    <t>Australia_Mataranka</t>
+  </si>
+  <si>
+    <t>Argonne</t>
+  </si>
+  <si>
+    <t>LATITUDE_DD</t>
+  </si>
+  <si>
+    <t>LONGITUDE_DD</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>Auf "Yukon" umbenennen</t>
+  </si>
+  <si>
+    <t>CONDUCTIVITY</t>
+  </si>
+  <si>
+    <t>CA_MG_L</t>
+  </si>
+  <si>
+    <t>MG_MG_L</t>
+  </si>
+  <si>
+    <t>NA_MG_L</t>
+  </si>
+  <si>
+    <t>CL_MG_L</t>
+  </si>
+  <si>
+    <t>SO4_MG_L</t>
+  </si>
+  <si>
+    <t>HCO3_MG_L</t>
+  </si>
+  <si>
+    <t>K_MG_L</t>
+  </si>
+  <si>
+    <t>F_MG_L</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Geothermal province</t>
+  </si>
+  <si>
+    <t>Hot spring</t>
+  </si>
+  <si>
+    <t>Na (mg/L)</t>
+  </si>
+  <si>
+    <t>Mg (mg/L)</t>
+  </si>
+  <si>
+    <t>Ca (mg/L)</t>
+  </si>
+  <si>
+    <t>Cl (mg/L)</t>
+  </si>
+  <si>
+    <t>SO4 (mg/L)</t>
+  </si>
+  <si>
+    <t>HCO3 (mg/L)</t>
+  </si>
+  <si>
+    <t>K (mg/L)</t>
+  </si>
+  <si>
+    <t>Fe (mg/L)</t>
+  </si>
+  <si>
+    <t>Mn (mg/L)</t>
+  </si>
+  <si>
+    <t>Fe</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Herleiten aus Standort</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>in mg/L, muss in mmol/L</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>samples</t>
+  </si>
+  <si>
+    <t>Temp_C</t>
+  </si>
+  <si>
+    <t>EC_uS_cm</t>
+  </si>
+  <si>
+    <t>muss herausgefunden werden</t>
+  </si>
+  <si>
+    <t>TDS_mg_L</t>
+  </si>
+  <si>
+    <t>Cl_mg_L</t>
+  </si>
+  <si>
+    <t>SO4_mg_L</t>
+  </si>
+  <si>
+    <t>HCO3_mg_L</t>
+  </si>
+  <si>
+    <t>K_mg_L</t>
+  </si>
+  <si>
+    <t>Fe_mg_L</t>
+  </si>
+  <si>
+    <t>F_mg_L</t>
+  </si>
+  <si>
+    <t>NO3_mg_L</t>
+  </si>
+  <si>
+    <t>Ca_mg_L</t>
+  </si>
+  <si>
+    <t>Mg_mg_L</t>
+  </si>
+  <si>
+    <t>Na_mg_L</t>
+  </si>
+  <si>
+    <t>"&lt;" und ND müssen eliminiert werden</t>
+  </si>
+  <si>
+    <t>CLA flow path</t>
+  </si>
+  <si>
+    <t>Bore/Spring</t>
+  </si>
+  <si>
+    <t>Alkalinity (meq/L)</t>
+  </si>
+  <si>
+    <t>Database_number</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 3</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 4</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 2</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 1</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 5</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 6</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 9</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 7</t>
+  </si>
+  <si>
+    <t>SHEET1</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 8</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 10</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 11</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 12</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer 13</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>All Data</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Depth(ft)</t>
+  </si>
+  <si>
+    <t>Temperature(C)</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>NH4(N)</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>NO3(n)</t>
+  </si>
+  <si>
+    <t>BI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -928,8 +1175,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -978,8 +1231,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1380,11 +1639,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1450,7 +1746,26 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2027,6 +2342,2996 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D0DECE-F944-4166-B9C2-A35BFCA53CD3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD637B6-31BE-4132-B6EC-16CB48802776}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="39.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="29.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="23" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="50"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="50"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="53"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="50"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>307</v>
+      </c>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93712737-46D7-4E79-A9CA-D5886A560D55}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="76" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D5" t="s">
+        <v>325</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="76" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="76" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" t="s">
+        <v>325</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>325</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" t="s">
+        <v>325</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" t="s">
+        <v>325</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>307</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D19" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D20" t="s">
+        <v>325</v>
+      </c>
+      <c r="E20" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E21" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>325</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D24" t="s">
+        <v>325</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>334</v>
+      </c>
+      <c r="D27" t="s">
+        <v>325</v>
+      </c>
+      <c r="E27" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D30" t="s">
+        <v>325</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>325</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD005A73-F242-4F7A-BB2E-2697CC11F714}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D11" t="s">
+        <v>360</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" t="s">
+        <v>360</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>360</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" t="s">
+        <v>360</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" t="s">
+        <v>360</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
+        <v>360</v>
+      </c>
+      <c r="E20" t="s">
+        <v>307</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>360</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" t="s">
+        <v>360</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>360</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>360</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D26" t="s">
+        <v>360</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" t="s">
+        <v>360</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28" s="23"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>360</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D30" t="s">
+        <v>360</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>325</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>357</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="64" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D46C7FC-4F92-409B-95F3-5697C13BE790}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" t="s">
+        <v>270</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" t="s">
+        <v>270</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" t="s">
+        <v>270</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" t="s">
+        <v>270</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>359</v>
+      </c>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F02165-A680-4281-B1A6-6E8AF394A478}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="59.85546875" customWidth="1"/>
+    <col min="7" max="7" width="67.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>185</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" s="62" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>346</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="91" scale="38" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAC61E6-50DF-405D-A52F-EDADE72AA266}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2035,7 +5340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8011DF-EFF6-4FCD-84E2-B9EE254EAD4E}">
   <dimension ref="B2:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2051,7 +5356,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2077,7 +5382,7 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>38</v>
@@ -2193,7 +5498,7 @@
       <c r="C16" s="6"/>
       <c r="F16" s="41"/>
       <c r="G16" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2205,7 +5510,7 @@
       <c r="E17" s="33"/>
       <c r="F17" s="40"/>
       <c r="G17" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -2215,7 +5520,7 @@
       <c r="C18" s="6"/>
       <c r="F18" s="41"/>
       <c r="G18" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -2225,7 +5530,7 @@
       <c r="C19" s="6"/>
       <c r="F19" s="41"/>
       <c r="G19" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -2235,7 +5540,7 @@
       <c r="C20" s="6"/>
       <c r="F20" s="41"/>
       <c r="G20" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -2245,7 +5550,7 @@
       <c r="C21" s="6"/>
       <c r="F21" s="41"/>
       <c r="G21" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -2257,7 +5562,7 @@
       <c r="E22" s="37"/>
       <c r="F22" s="46"/>
       <c r="G22" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -2268,7 +5573,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="23"/>
       <c r="G23" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -2279,7 +5584,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="23"/>
       <c r="G24" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -2290,7 +5595,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -2301,7 +5606,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
@@ -2312,7 +5617,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -2323,7 +5628,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
@@ -2334,7 +5639,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -2345,7 +5650,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
@@ -2356,7 +5661,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2368,7 +5673,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -2386,25 +5691,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D46C7FC-4F92-409B-95F3-5697C13BE790}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28484C-C581-4663-8490-31B7BD27263E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.140625" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>288</v>
+        <v>194</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2427,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>271</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
@@ -2445,13 +5750,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>273</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>85</v>
@@ -2459,73 +5764,89 @@
       <c r="G5" s="23"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29" t="s">
-        <v>274</v>
-      </c>
+      <c r="C6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29" t="s">
-        <v>274</v>
-      </c>
+      <c r="C7" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="29"/>
-      <c r="G8" s="29" t="s">
-        <v>286</v>
-      </c>
+      <c r="G8" s="23"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
       <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
+      <c r="G9" s="23"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D10" s="15"/>
       <c r="E10" s="16"/>
       <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
+      <c r="G10" s="23"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>85</v>
@@ -2533,14 +5854,22 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
+      <c r="C12" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="23"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
@@ -2550,10 +5879,10 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>85</v>
@@ -2564,55 +5893,55 @@
       <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
+      <c r="F14" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="23"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D15" t="s">
-        <v>272</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>85</v>
-      </c>
+      <c r="C15" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
       <c r="G15" s="23"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="13"/>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="23"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>281</v>
+        <v>108</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>85</v>
+        <v>140</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>112</v>
       </c>
       <c r="G17" s="23"/>
     </row>
@@ -2621,16 +5950,16 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>272</v>
-      </c>
-      <c r="E18" s="65" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>85</v>
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="G18" s="23"/>
     </row>
@@ -2639,16 +5968,16 @@
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>283</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>272</v>
-      </c>
-      <c r="E19" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>85</v>
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="G19" s="23"/>
     </row>
@@ -2657,16 +5986,16 @@
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>272</v>
-      </c>
-      <c r="E20" s="65" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>85</v>
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="G20" s="23"/>
     </row>
@@ -2675,16 +6004,16 @@
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>278</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>272</v>
-      </c>
-      <c r="E21" s="65" t="s">
-        <v>144</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>85</v>
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="G21" s="23"/>
     </row>
@@ -2693,16 +6022,16 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>279</v>
+        <v>142</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>112</v>
       </c>
       <c r="G22" s="23"/>
     </row>
@@ -2711,19 +6040,19 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D23" t="s">
-        <v>272</v>
+        <v>143</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>134</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>287</v>
+        <v>94</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -2731,16 +6060,16 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>280</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>85</v>
+        <v>144</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="G24" s="23"/>
     </row>
@@ -2749,112 +6078,179 @@
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>285</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" s="23"/>
+        <v>95</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="13"/>
+      <c r="C26" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D26" s="15"/>
       <c r="E26" s="16"/>
       <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
+      <c r="G26" s="23"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
+      <c r="C27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
+      <c r="C28" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
+      <c r="C29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="23"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
+      <c r="C30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13"/>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
+      <c r="F31" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="31"/>
+      <c r="C32" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="56"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A059286-C8A1-4672-9077-497707963BB5}">
-  <dimension ref="B2:G32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783802C3-70F2-469E-9F15-66886A2B472E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2877,592 +6273,1044 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>219</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>222</v>
+        <v>89</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>221</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>225</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>235</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>226</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>235</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="23"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D9" t="s">
-        <v>220</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>230</v>
-      </c>
+      <c r="C9" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="23"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>230</v>
-      </c>
+      <c r="C10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="23"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="23"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D14" t="s">
-        <v>220</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="23"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>239</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>241</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="23"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D16" t="s">
-        <v>220</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="23"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="44" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>242</v>
+        <v>108</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="F17" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="23"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>244</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
+        <v>90</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G18" s="23"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>245</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" t="s">
-        <v>54</v>
+        <v>90</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G19" s="23"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E20" t="s">
-        <v>56</v>
+        <v>90</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G20" s="23"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E21" t="s">
-        <v>58</v>
+        <v>90</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>220</v>
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="23"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" t="s">
-        <v>220</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="23"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D27" t="s">
-        <v>220</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="23"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D28" t="s">
-        <v>220</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C28" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="23"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>256</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F29" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>223</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="23"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C30" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D31" t="s">
-        <v>220</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="F32" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>223</v>
+      <c r="C32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="7" max="7" width="33.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="23"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6DB8F-FD5C-4693-8887-04E42CDC7E06}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -3861,32 +7709,46 @@
       <c r="F32" s="31"/>
       <c r="G32" s="31"/>
     </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A85E326E-8D3B-4CF5-91CA-01DA393CBB40}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A059286-C8A1-4672-9077-497707963BB5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="59.85546875" customWidth="1"/>
-    <col min="7" max="7" width="67.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -3909,237 +7771,279 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="23"/>
+      <c r="G5" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" s="23"/>
+      <c r="F6" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="23"/>
+      <c r="F7" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F8" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="23" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>156</v>
+        <v>231</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="F10" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="23" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="23"/>
+        <v>85</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
+      <c r="C12" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
+      <c r="C14" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="G15" s="61" t="s">
-        <v>191</v>
+        <v>220</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="29"/>
+      <c r="C16" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="F17" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="G17" s="61" t="s">
-        <v>191</v>
+      <c r="G17" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -4147,19 +8051,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G18" s="61" t="s">
-        <v>191</v>
+      <c r="G18" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -4167,19 +8071,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>54</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G19" s="61" t="s">
-        <v>191</v>
+      <c r="G19" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -4187,19 +8091,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F20" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G20" s="61" t="s">
-        <v>191</v>
+      <c r="G20" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -4207,19 +8111,19 @@
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="F21" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="61" t="s">
-        <v>191</v>
+      <c r="G21" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -4227,19 +8131,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="F22" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="G22" s="61" t="s">
-        <v>191</v>
+      <c r="G22" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -4247,19 +8151,19 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" t="s">
-        <v>134</v>
+        <v>250</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>220</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G23" s="61" t="s">
-        <v>191</v>
+      <c r="G23" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -4267,19 +8171,19 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F24" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G24" s="61" t="s">
-        <v>191</v>
+      <c r="G24" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -4287,19 +8191,19 @@
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="G25" s="61" t="s">
-        <v>191</v>
+      <c r="G25" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -4307,19 +8211,19 @@
         <v>20</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F26" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="G26" s="61" t="s">
-        <v>191</v>
+      <c r="G26" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
@@ -4327,19 +8231,19 @@
         <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="F27" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G27" s="61" t="s">
-        <v>191</v>
+      <c r="G27" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -4347,19 +8251,19 @@
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G28" s="61" t="s">
-        <v>191</v>
+      <c r="G28" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
@@ -4367,19 +8271,19 @@
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F29" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="F29" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="G29" s="61" t="s">
-        <v>191</v>
+      <c r="G29" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -4387,79 +8291,93 @@
         <v>24</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="F30" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="G30" s="61" t="s">
-        <v>191</v>
+      <c r="G30" s="23" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
+      <c r="C31" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D31" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F32" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="62" t="s">
-        <v>191</v>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="91" scale="38" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC28484C-C581-4663-8490-31B7BD27263E}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18FF336-46F8-4D37-8622-02C18144015A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>194</v>
+        <v>288</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -4478,980 +8396,441 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="23"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="23" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>130</v>
+        <v>296</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>132</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="G6" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>133</v>
+        <v>295</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="23"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="23"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="23"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>138</v>
+        <v>298</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="E12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="G12" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="23"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>7</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="23"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="50" t="s">
-        <v>139</v>
-      </c>
+      <c r="C15" s="50"/>
       <c r="D15" s="51"/>
       <c r="E15" s="52"/>
       <c r="F15" s="53"/>
-      <c r="G15" s="23"/>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="23"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>108</v>
+        <v>301</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="F17" s="40"/>
+      <c r="G17" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="23"/>
+        <v>80</v>
+      </c>
+      <c r="F18" s="41"/>
+      <c r="G18" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>113</v>
+        <v>299</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="23"/>
+        <v>97</v>
+      </c>
+      <c r="F19" s="41"/>
+      <c r="G19" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>115</v>
+        <v>302</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="23"/>
+        <v>307</v>
+      </c>
+      <c r="F20" s="41"/>
+      <c r="G20" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>117</v>
+        <v>303</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G21" s="23"/>
+        <v>151</v>
+      </c>
+      <c r="F21" s="41"/>
+      <c r="G21" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>142</v>
+        <v>304</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="23"/>
+        <v>353</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="46"/>
+      <c r="G22" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="61" t="s">
-        <v>190</v>
-      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="23"/>
+        <v>305</v>
+      </c>
+      <c r="D24" s="74" t="s">
+        <v>353</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="26" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D25" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="61" t="s">
-        <v>190</v>
-      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="23"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G27" s="61" t="s">
-        <v>190</v>
-      </c>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="61" t="s">
-        <v>190</v>
-      </c>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>124</v>
+        <v>306</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="E29" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="23"/>
+      <c r="G29" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="G29" s="23"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G30" s="23"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="23"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="56"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32" s="24"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>353</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>352</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783802C3-70F2-469E-9F15-66886A2B472E}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B2:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="40.140625" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" customWidth="1"/>
-    <col min="6" max="6" width="29.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="29"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="29"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="29"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="29"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="29"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="29"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="29"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="29"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="29"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="29"/>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="31"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="62" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AFA507D-96A5-4094-AEF4-E3855A0C365E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" customWidth="1"/>
+    <col min="7" max="7" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -5465,478 +8844,433 @@
       <c r="F3" s="25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>33</v>
+        <v>309</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="50"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="C10" s="50"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
+      <c r="C11" s="50"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C12" s="50"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="44" t="s">
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="53"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>55</v>
+        <v>310</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="45" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>54</v>
+        <v>311</v>
+      </c>
+      <c r="D18" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>80</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>312</v>
+      </c>
+      <c r="D19" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>97</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>60</v>
+        <v>313</v>
+      </c>
+      <c r="D20" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>151</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>66</v>
+        <v>314</v>
+      </c>
+      <c r="D21" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>227</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>63</v>
+        <v>315</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C23" s="50"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>57</v>
+        <v>316</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>58</v>
+        <v>134</v>
+      </c>
+      <c r="E24" s="74" t="s">
+        <v>144</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="19" t="s">
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="23"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>67</v>
+        <v>317</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>68</v>
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>69</v>
+        <v>318</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>70</v>
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>77</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G28" s="23"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="19" t="s">
+      <c r="C29" s="50"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="23"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="23"/>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="20" t="s">
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="24"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>307</v>
+      </c>
+      <c r="F33" s="81"/>
+      <c r="G33" s="82" t="s">
+        <v>354</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="61" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FCC783-BE1B-4338-8651-9368BB735F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C88B03-3B4D-40B1-903C-2C54575119F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="371">
   <si>
     <t>location</t>
   </si>
@@ -1161,6 +1161,9 @@
   </si>
   <si>
     <t>BI</t>
+  </si>
+  <si>
+    <t>hinzugefügt, Nummer XY</t>
   </si>
 </sst>
 </file>
@@ -1680,7 +1683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1754,15 +1757,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2046,7 +2043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40B4A1F-305E-4A10-9B22-5AB123015450}">
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -2335,6 +2332,20 @@
       <c r="E32" s="5"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="75" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
+        <v>370</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -2757,20 +2768,20 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3008,13 +3019,13 @@
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="75" t="s">
+      <c r="C18" s="73" t="s">
         <v>180</v>
       </c>
       <c r="D18" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="74" t="s">
+      <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="26" t="s">
@@ -3028,13 +3039,13 @@
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="73" t="s">
         <v>174</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="74" t="s">
+      <c r="E19" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="26" t="s">
@@ -3048,13 +3059,13 @@
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="75" t="s">
+      <c r="C20" s="73" t="s">
         <v>167</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="74" t="s">
+      <c r="E20" t="s">
         <v>140</v>
       </c>
       <c r="F20" s="26" t="s">
@@ -3074,7 +3085,7 @@
       <c r="D21" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="74" t="s">
+      <c r="E21" t="s">
         <v>144</v>
       </c>
       <c r="F21" s="26" t="s">
@@ -3215,20 +3226,20 @@
       <c r="G32" s="69"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="75" t="s">
         <v>307</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>355</v>
       </c>
     </row>
@@ -3283,7 +3294,7 @@
       <c r="D4" s="15"/>
       <c r="E4" s="16"/>
       <c r="F4" s="29"/>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="23" t="s">
         <v>328</v>
       </c>
     </row>
@@ -3313,7 +3324,7 @@
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="29"/>
-      <c r="G6" s="76" t="s">
+      <c r="G6" s="23" t="s">
         <v>328</v>
       </c>
     </row>
@@ -3325,7 +3336,7 @@
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="29"/>
-      <c r="G7" s="76" t="s">
+      <c r="G7" s="23" t="s">
         <v>328</v>
       </c>
     </row>
@@ -3481,7 +3492,7 @@
       <c r="D18" t="s">
         <v>325</v>
       </c>
-      <c r="E18" s="74" t="s">
+      <c r="E18" t="s">
         <v>307</v>
       </c>
       <c r="F18" s="26" t="s">
@@ -3501,7 +3512,7 @@
       <c r="D19" t="s">
         <v>325</v>
       </c>
-      <c r="E19" s="74" t="s">
+      <c r="E19" t="s">
         <v>89</v>
       </c>
       <c r="F19" s="26" t="s">
@@ -3521,7 +3532,7 @@
       <c r="D20" t="s">
         <v>325</v>
       </c>
-      <c r="E20" s="74" t="s">
+      <c r="E20" t="s">
         <v>144</v>
       </c>
       <c r="F20" s="26" t="s">
@@ -3541,7 +3552,7 @@
       <c r="D21" t="s">
         <v>325</v>
       </c>
-      <c r="E21" s="74" t="s">
+      <c r="E21" t="s">
         <v>77</v>
       </c>
       <c r="F21" s="26" t="s">
@@ -3622,16 +3633,16 @@
       <c r="G26" s="29"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="78" t="s">
+      <c r="C27" t="s">
         <v>334</v>
       </c>
       <c r="D27" t="s">
         <v>325</v>
       </c>
-      <c r="E27" s="79" t="s">
+      <c r="E27" s="2" t="s">
         <v>287</v>
       </c>
       <c r="F27" s="26" t="s">
@@ -3712,20 +3723,20 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>325</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>356</v>
       </c>
     </row>
@@ -4239,18 +4250,18 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>325</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4708,20 +4719,20 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>270</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="75" t="s">
         <v>359</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>358</v>
       </c>
     </row>
@@ -5308,20 +5319,20 @@
       </c>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6210,18 +6221,18 @@
       <c r="G32" s="24"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>348</v>
       </c>
     </row>
@@ -6727,18 +6738,18 @@
       <c r="G32" s="24"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>347</v>
       </c>
     </row>
@@ -7284,18 +7295,18 @@
       <c r="G32" s="24"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>345</v>
       </c>
     </row>
@@ -7710,16 +7721,16 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>349</v>
       </c>
     </row>
@@ -8337,18 +8348,18 @@
       <c r="G32" s="69"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>220</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>350</v>
       </c>
     </row>
@@ -8690,7 +8701,7 @@
       <c r="C24" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D24" s="74" t="s">
+      <c r="D24" t="s">
         <v>353</v>
       </c>
       <c r="E24" t="s">
@@ -8790,18 +8801,18 @@
       <c r="G32" s="69"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>353</v>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>352</v>
       </c>
     </row>
@@ -9043,7 +9054,7 @@
       <c r="C18" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="D18" s="73" t="s">
+      <c r="D18" t="s">
         <v>134</v>
       </c>
       <c r="E18" t="s">
@@ -9061,7 +9072,7 @@
       <c r="C19" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" t="s">
         <v>134</v>
       </c>
       <c r="E19" t="s">
@@ -9079,7 +9090,7 @@
       <c r="C20" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" t="s">
         <v>134</v>
       </c>
       <c r="E20" t="s">
@@ -9097,7 +9108,7 @@
       <c r="C21" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="D21" t="s">
         <v>134</v>
       </c>
       <c r="E21" t="s">
@@ -9146,7 +9157,7 @@
       <c r="D24" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="74" t="s">
+      <c r="E24" t="s">
         <v>144</v>
       </c>
       <c r="F24" s="26" t="s">
@@ -9251,20 +9262,20 @@
       <c r="G32" s="69"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="74" t="s">
         <v>344</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="81" t="s">
+      <c r="D33" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="75" t="s">
         <v>307</v>
       </c>
-      <c r="F33" s="81"/>
-      <c r="G33" s="82" t="s">
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>354</v>
       </c>
     </row>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C88B03-3B4D-40B1-903C-2C54575119F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797A48E8-599E-4C5B-BACF-4D8EEE0BE0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="408">
   <si>
     <t>location</t>
   </si>
@@ -446,9 +446,6 @@
     <t>Site</t>
   </si>
   <si>
-    <t>nicht vorhanden - IDAHO eintragen</t>
-  </si>
-  <si>
     <t>Longitude</t>
   </si>
   <si>
@@ -908,9 +905,6 @@
     <t>Schätzen aus Location_name (grob)</t>
   </si>
   <si>
-    <t>liegt in ppb vor, müsste in ppm vorliegen</t>
-  </si>
-  <si>
     <t>SVZ_Chile</t>
   </si>
   <si>
@@ -1022,9 +1016,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>in mg/L, muss in mmol/L</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -1142,35 +1133,571 @@
     <t>State</t>
   </si>
   <si>
-    <t>Depth(ft)</t>
-  </si>
-  <si>
-    <t>Temperature(C)</t>
-  </si>
-  <si>
     <t>AE</t>
   </si>
   <si>
-    <t>NH4(N)</t>
-  </si>
-  <si>
     <t>AA</t>
   </si>
   <si>
-    <t>NO3(n)</t>
-  </si>
-  <si>
     <t>BI</t>
   </si>
   <si>
     <t>hinzugefügt, Nummer XY</t>
+  </si>
+  <si>
+    <t>Depth_ft</t>
+  </si>
+  <si>
+    <t>NO3_N</t>
+  </si>
+  <si>
+    <t>NH4_N</t>
+  </si>
+  <si>
+    <t>nicht vorhanden - Southeast Tibet Pleateau eintragen</t>
+  </si>
+  <si>
+    <t>Southeast Tibet Pleateau über Jupyter einfügen</t>
+  </si>
+  <si>
+    <t>well_depth_(m) -&gt; well_depth_m</t>
+  </si>
+  <si>
+    <t>Funktion zum Mapping erkennt keine</t>
+  </si>
+  <si>
+    <t>Sonderzeichen außer - und _, deshalb manuelle</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EC_(S_m^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EC_S_m-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">temperature_(degr_C) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>temperature_degr_C</t>
+    </r>
+  </si>
+  <si>
+    <t>Umänderung in Excel ohne Klammern,^ und Leerzeichen</t>
+  </si>
+  <si>
+    <r>
+      <t>TDS_(mg L^-1) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TDS_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Na_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Na_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mg_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mg_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ca_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ca_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cl_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cl_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SO4_(mg L^-1) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SO4_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>HCO3_(mg L^-1) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> HCO3_mg L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Li_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Li_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">K_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NH4_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">F_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NO3_(mg L^-1) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NO3_mg_L-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Total dissolved solids calculated -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Total_dissolved_solids_calculated</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coordinates H -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coordinates_H</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Coordinates R -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Coordinates_R</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">K (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>K_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fe (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fe_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mn (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mn_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Na (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Na_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mg (mg/L) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mg_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ca (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ca_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cl (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cl_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SO4 (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SO4_mg-l</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HCO3 (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HCO3_mg-l</t>
+    </r>
+  </si>
+  <si>
+    <t>Geothermal province -&gt; Geothermal_province</t>
+  </si>
+  <si>
+    <t>Nein, da HCO3 einwertig ist gilt meq/L = mmol/L</t>
+  </si>
+  <si>
+    <r>
+      <t>CLA flow path -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CLA_flow_path</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bore/Spring -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bore_Spring</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mg (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mg_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ca (mg/L) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ca_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SO4 (mg/L) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SO4_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alkalinity (meq/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkalinity_meq-L</t>
+    </r>
+  </si>
+  <si>
+    <t>liegt in ppb vor, müsste in ppm vorliegen, Faktor / 1.000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1184,8 +1711,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1240,8 +1775,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1679,11 +2220,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1763,6 +2317,17 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2071,7 +2636,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -2335,16 +2900,16 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75"/>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2364,14 +2929,14 @@
     <col min="3" max="3" width="31.85546875" customWidth="1"/>
     <col min="4" max="4" width="27.5703125" customWidth="1"/>
     <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="31.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" customWidth="1"/>
+    <col min="6" max="6" width="48.28515625" customWidth="1"/>
+    <col min="7" max="7" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2386,36 +2951,38 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>341</v>
+      <c r="C4" s="80" t="s">
+        <v>338</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="61" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>342</v>
+      <c r="C5" s="80" t="s">
+        <v>339</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>103</v>
@@ -2423,20 +2990,22 @@
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="23"/>
+      <c r="G5" s="61" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
         <v>133</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>85</v>
@@ -2448,10 +3017,10 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>38</v>
@@ -2555,109 +3124,121 @@
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>310</v>
+      <c r="C17" s="81" t="s">
+        <v>308</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>311</v>
+      <c r="C18" s="80" t="s">
+        <v>309</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G18" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>312</v>
+      <c r="C19" s="80" t="s">
+        <v>310</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>313</v>
+      <c r="C20" s="80" t="s">
+        <v>311</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G20" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>314</v>
+      <c r="C21" s="80" t="s">
+        <v>312</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>97</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G21" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>343</v>
+      <c r="C22" s="82" t="s">
+        <v>340</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="23"/>
+      <c r="F22" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="19" t="s">
@@ -2673,19 +3254,21 @@
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>316</v>
+      <c r="C24" s="80" t="s">
+        <v>314</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G24" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
@@ -2745,7 +3328,9 @@
       <c r="D30" s="15"/>
       <c r="E30" s="16"/>
       <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
+      <c r="G30" s="77" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
@@ -2755,7 +3340,9 @@
       <c r="D31" s="15"/>
       <c r="E31" s="16"/>
       <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
+      <c r="G31" s="78" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="20" t="s">
@@ -2765,29 +3352,31 @@
       <c r="D32" s="17"/>
       <c r="E32" s="18"/>
       <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
+      <c r="G32" s="78" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="71" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2810,7 +3399,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -2825,7 +3414,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -2843,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="23"/>
@@ -2858,7 +3447,7 @@
       <c r="E6" s="52"/>
       <c r="F6" s="53"/>
       <c r="G6" s="23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2870,7 +3459,7 @@
       <c r="E7" s="52"/>
       <c r="F7" s="53"/>
       <c r="G7" s="23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2908,10 +3497,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>34</v>
@@ -2926,10 +3515,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>38</v>
@@ -2944,10 +3533,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>37</v>
@@ -2972,10 +3561,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>77</v>
@@ -3000,120 +3589,108 @@
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D17" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>135</v>
-      </c>
       <c r="F17" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G17" s="23"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G18" s="23"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G19" s="23"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G20" s="23"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>80</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="70" t="s">
@@ -3130,20 +3707,18 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>323</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="70" t="s">
@@ -3227,25 +3802,25 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="87" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3268,7 +3843,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -3283,7 +3858,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -3295,7 +3870,7 @@
       <c r="E4" s="16"/>
       <c r="F4" s="29"/>
       <c r="G4" s="23" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -3303,10 +3878,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>103</v>
@@ -3325,7 +3900,7 @@
       <c r="E6" s="16"/>
       <c r="F6" s="29"/>
       <c r="G6" s="23" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -3337,7 +3912,7 @@
       <c r="E7" s="16"/>
       <c r="F7" s="29"/>
       <c r="G7" s="23" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -3375,13 +3950,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>85</v>
@@ -3393,10 +3968,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>38</v>
@@ -3414,7 +3989,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>34</v>
@@ -3439,16 +4014,16 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G15" s="23"/>
     </row>
@@ -3467,19 +4042,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -3487,19 +4062,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -3507,19 +4082,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E19" t="s">
         <v>89</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -3527,19 +4102,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D20" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -3547,19 +4122,19 @@
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -3567,19 +4142,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>97</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3597,19 +4172,19 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D24" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -3637,19 +4212,19 @@
         <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D27" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -3667,10 +4242,10 @@
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D29" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>102</v>
@@ -3679,7 +4254,7 @@
         <v>123</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -3687,19 +4262,19 @@
         <v>24</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D30" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
@@ -3724,25 +4299,25 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3765,7 +4340,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -3780,7 +4355,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -3788,13 +4363,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
@@ -3806,13 +4381,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>85</v>
@@ -3824,10 +4399,10 @@
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>37</v>
@@ -3842,10 +4417,10 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>38</v>
@@ -3860,13 +4435,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F8" s="26" t="s">
         <v>100</v>
@@ -3898,10 +4473,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>364</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -3929,7 +4504,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>96</v>
@@ -3954,13 +4529,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F15" s="28" t="s">
         <v>85</v>
@@ -3982,16 +4557,16 @@
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>97</v>
       </c>
       <c r="F17" s="60" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G17" s="23"/>
     </row>
@@ -4000,16 +4575,16 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G18" s="23"/>
     </row>
@@ -4018,16 +4593,16 @@
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G19" s="23"/>
     </row>
@@ -4036,16 +4611,16 @@
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" s="23"/>
     </row>
@@ -4054,16 +4629,16 @@
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G21" s="23"/>
     </row>
@@ -4072,16 +4647,16 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G22" s="23"/>
     </row>
@@ -4090,16 +4665,16 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D23" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G23" s="23"/>
     </row>
@@ -4108,16 +4683,16 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G24" s="23"/>
     </row>
@@ -4126,13 +4701,13 @@
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D25" t="s">
+        <v>357</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>123</v>
@@ -4147,10 +4722,10 @@
         <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F26" s="26" t="s">
         <v>123</v>
@@ -4162,16 +4737,16 @@
         <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D27" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G27" s="23"/>
     </row>
@@ -4180,16 +4755,16 @@
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G28" s="23"/>
     </row>
@@ -4198,10 +4773,10 @@
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>94</v>
@@ -4216,16 +4791,16 @@
         <v>24</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D30" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G30" s="23"/>
     </row>
@@ -4251,23 +4826,23 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="64" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="85" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4284,13 +4859,13 @@
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="5" width="26.85546875" customWidth="1"/>
     <col min="6" max="6" width="26.42578125" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="56.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -4305,7 +4880,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -4313,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" t="s">
         <v>269</v>
-      </c>
-      <c r="D4" t="s">
-        <v>270</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>34</v>
@@ -4331,10 +4906,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>38</v>
@@ -4353,7 +4928,7 @@
       <c r="E6" s="16"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -4365,7 +4940,7 @@
       <c r="E7" s="16"/>
       <c r="F7" s="29"/>
       <c r="G7" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -4377,7 +4952,7 @@
       <c r="E8" s="16"/>
       <c r="F8" s="29"/>
       <c r="G8" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -4405,13 +4980,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>85</v>
@@ -4436,10 +5011,10 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>85</v>
@@ -4461,10 +5036,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>32</v>
@@ -4489,10 +5064,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>80</v>
@@ -4507,10 +5082,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E18" t="s">
         <v>102</v>
@@ -4525,10 +5100,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
@@ -4543,13 +5118,13 @@
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F20" s="28" t="s">
         <v>85</v>
@@ -4561,13 +5136,13 @@
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F21" s="28" t="s">
         <v>85</v>
@@ -4579,10 +5154,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>97</v>
@@ -4597,19 +5172,19 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>285</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -4617,10 +5192,10 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>39</v>
@@ -4635,13 +5210,13 @@
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>85</v>
@@ -4720,25 +5295,25 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="66" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="81" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4770,7 +5345,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -4785,7 +5360,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -4793,10 +5368,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>80</v>
@@ -4811,10 +5386,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>89</v>
@@ -4829,13 +5404,13 @@
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>85</v>
@@ -4847,13 +5422,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>85</v>
@@ -4865,10 +5440,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>82</v>
@@ -4883,10 +5458,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>52</v>
@@ -4901,10 +5476,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>44</v>
@@ -4919,16 +5494,16 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G11" s="23"/>
     </row>
@@ -4949,10 +5524,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>64</v>
@@ -4979,19 +5554,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G15" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
@@ -5011,19 +5586,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>187</v>
-      </c>
       <c r="F17" s="60" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G17" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -5031,19 +5606,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>116</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G18" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -5051,19 +5626,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" t="s">
         <v>174</v>
       </c>
-      <c r="D19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" t="s">
-        <v>175</v>
-      </c>
       <c r="F19" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G19" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -5071,19 +5646,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>127</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -5091,19 +5666,19 @@
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G21" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -5111,19 +5686,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="37" t="s">
+      <c r="F22" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="43" t="s">
-        <v>166</v>
-      </c>
       <c r="G22" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -5131,19 +5706,19 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G23" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -5151,19 +5726,19 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G24" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -5171,19 +5746,19 @@
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G25" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -5191,19 +5766,19 @@
         <v>20</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G26" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
@@ -5211,19 +5786,19 @@
         <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F27" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G27" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -5231,19 +5806,19 @@
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G28" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
@@ -5251,19 +5826,19 @@
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G29" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -5271,19 +5846,19 @@
         <v>24</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G30" s="61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
@@ -5303,42 +5878,42 @@
         <v>26</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F32" s="59" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G32" s="62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="91" scale="38" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5367,7 +5942,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -5382,7 +5957,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -5393,7 +5968,7 @@
         <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>38</v>
@@ -5509,7 +6084,7 @@
       <c r="C16" s="6"/>
       <c r="F16" s="41"/>
       <c r="G16" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -5521,7 +6096,7 @@
       <c r="E17" s="33"/>
       <c r="F17" s="40"/>
       <c r="G17" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -5531,7 +6106,7 @@
       <c r="C18" s="6"/>
       <c r="F18" s="41"/>
       <c r="G18" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -5541,7 +6116,7 @@
       <c r="C19" s="6"/>
       <c r="F19" s="41"/>
       <c r="G19" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -5551,7 +6126,7 @@
       <c r="C20" s="6"/>
       <c r="F20" s="41"/>
       <c r="G20" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -5561,7 +6136,7 @@
       <c r="C21" s="6"/>
       <c r="F21" s="41"/>
       <c r="G21" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -5573,7 +6148,7 @@
       <c r="E22" s="37"/>
       <c r="F22" s="46"/>
       <c r="G22" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -5584,7 +6159,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="23"/>
       <c r="G23" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -5595,7 +6170,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="23"/>
       <c r="G24" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -5606,7 +6181,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -5617,7 +6192,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
@@ -5628,7 +6203,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -5639,7 +6214,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
@@ -5650,7 +6225,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -5661,7 +6236,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
@@ -5672,7 +6247,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5684,7 +6259,7 @@
       <c r="E32" s="5"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -5710,17 +6285,17 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="3" max="3" width="53.42578125" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="28.7109375" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="31" customWidth="1"/>
+    <col min="7" max="7" width="46.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -5735,7 +6310,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -5743,10 +6318,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>103</v>
@@ -5754,7 +6329,9 @@
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="23" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -5764,7 +6341,7 @@
         <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>34</v>
@@ -5779,10 +6356,10 @@
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>38</v>
@@ -5797,13 +6374,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
         <v>133</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>85</v>
@@ -5851,13 +6428,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="D11" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>85</v>
@@ -5869,10 +6446,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>96</v>
@@ -5890,7 +6467,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>32</v>
@@ -5910,7 +6487,7 @@
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G14" s="23"/>
     </row>
@@ -5919,7 +6496,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="52"/>
@@ -5946,10 +6523,10 @@
         <v>108</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F17" s="45" t="s">
         <v>112</v>
@@ -5964,7 +6541,7 @@
         <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>97</v>
@@ -5982,7 +6559,7 @@
         <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
         <v>80</v>
@@ -6000,7 +6577,7 @@
         <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>77</v>
@@ -6018,7 +6595,7 @@
         <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>102</v>
@@ -6033,10 +6610,10 @@
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>89</v>
@@ -6051,10 +6628,10 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>94</v>
@@ -6063,7 +6640,7 @@
         <v>112</v>
       </c>
       <c r="G23" s="61" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -6074,10 +6651,10 @@
         <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F24" s="26" t="s">
         <v>112</v>
@@ -6089,10 +6666,10 @@
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>95</v>
@@ -6101,7 +6678,7 @@
         <v>123</v>
       </c>
       <c r="G25" s="61" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
@@ -6121,19 +6698,19 @@
         <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F27" s="26" t="s">
         <v>112</v>
       </c>
       <c r="G27" s="61" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -6141,19 +6718,19 @@
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>112</v>
       </c>
       <c r="G28" s="61" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
@@ -6164,7 +6741,7 @@
         <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>39</v>
@@ -6179,13 +6756,13 @@
         <v>24</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D30" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="F30" s="26" t="s">
         <v>112</v>
@@ -6222,23 +6799,23 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="69" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6261,7 +6838,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -6276,7 +6853,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -6739,10 +7316,10 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
         <v>90</v>
@@ -6750,12 +7327,12 @@
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6778,7 +7355,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -6793,7 +7370,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -7296,10 +7873,10 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
         <v>31</v>
@@ -7307,12 +7884,12 @@
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="81" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7329,13 +7906,13 @@
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="27.140625" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="7" max="7" width="57.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -7350,7 +7927,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -7358,46 +7935,52 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="77" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="23"/>
+      <c r="G5" s="78" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="23"/>
+      <c r="G6" s="78" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="28" t="s">
@@ -7409,25 +7992,27 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>201</v>
+      <c r="C8" s="80" t="s">
+        <v>200</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="61" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G9" s="23"/>
     </row>
@@ -7447,27 +8032,31 @@
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>209</v>
+      <c r="C11" s="80" t="s">
+        <v>208</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="61" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>210</v>
+      <c r="C12" s="80" t="s">
+        <v>209</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="G12" s="23"/>
+        <v>216</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
@@ -7498,14 +8087,16 @@
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>211</v>
+      <c r="C15" s="80" t="s">
+        <v>210</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="G15" s="23"/>
+      <c r="G15" s="61" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="47" t="s">
@@ -7523,103 +8114,119 @@
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>202</v>
+      <c r="C17" s="81" t="s">
+        <v>201</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
       <c r="F17" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="23"/>
+      <c r="G17" s="61" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>204</v>
+      <c r="C18" s="80" t="s">
+        <v>203</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G18" s="23"/>
+      <c r="G18" s="61" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>203</v>
+      <c r="C19" s="80" t="s">
+        <v>202</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="23"/>
+      <c r="G19" s="61" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>205</v>
+      <c r="C20" s="80" t="s">
+        <v>204</v>
       </c>
       <c r="F20" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G20" s="23"/>
+      <c r="G20" s="61" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>207</v>
+      <c r="C21" s="80" t="s">
+        <v>206</v>
       </c>
       <c r="F21" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="61" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>206</v>
+      <c r="C22" s="82" t="s">
+        <v>205</v>
       </c>
       <c r="D22" s="36"/>
       <c r="E22" s="37"/>
       <c r="F22" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="23"/>
+      <c r="G22" s="61" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>208</v>
+      <c r="C23" s="80" t="s">
+        <v>207</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="61" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>212</v>
+      <c r="C24" s="80" t="s">
+        <v>211</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G24" s="23"/>
+      <c r="G24" s="61" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="19" t="s">
@@ -7637,14 +8244,16 @@
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>213</v>
+      <c r="C26" s="80" t="s">
+        <v>212</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G26" s="23"/>
+        <v>180</v>
+      </c>
+      <c r="G26" s="61" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
@@ -7674,27 +8283,31 @@
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>214</v>
+      <c r="C29" s="80" t="s">
+        <v>213</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="G29" s="23"/>
+        <v>180</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>215</v>
+      <c r="C30" s="80" t="s">
+        <v>214</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="G30" s="23"/>
+      <c r="G30" s="61" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
@@ -7722,21 +8335,21 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75"/>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="79" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7745,7 +8358,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.28515625" customWidth="1"/>
@@ -7753,13 +8366,14 @@
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="29.5703125" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" customWidth="1"/>
+    <col min="8" max="8" width="63.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -7774,38 +8388,42 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" t="s">
         <v>219</v>
       </c>
-      <c r="D4" t="s">
-        <v>220</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H4" s="23"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>34</v>
@@ -7814,58 +8432,65 @@
         <v>85</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H5" s="23"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>225</v>
+      <c r="C6" s="80" t="s">
+        <v>224</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>226</v>
+      <c r="C7" s="80" t="s">
+        <v>225</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>97</v>
@@ -7874,38 +8499,40 @@
         <v>85</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H8" s="23"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="H9" s="23"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>89</v>
@@ -7914,38 +8541,40 @@
         <v>85</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="H10" s="23"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="D11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H11" s="23"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>42</v>
@@ -7954,10 +8583,11 @@
         <v>85</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H12" s="23"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
@@ -7965,379 +8595,406 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H13" s="23"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D14" t="s">
-        <v>220</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="F14" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="80" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D15" t="s">
-        <v>220</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="F15" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F16" s="64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H16" s="23"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>242</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>243</v>
-      </c>
       <c r="F17" s="60" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H18" s="23"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
         <v>54</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
         <v>56</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H20" s="23"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E21" t="s">
         <v>58</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H21" s="23"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="D22" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>249</v>
-      </c>
       <c r="F22" s="43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H22" s="23"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H23" s="23"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H24" s="23"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H25" s="23"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H26" s="23"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H27" s="23"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H28" s="23"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H29" s="77" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="H30" s="78" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="H31" s="78" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="65" t="s">
         <v>26</v>
       </c>
@@ -8346,26 +9003,28 @@
       <c r="E32" s="68"/>
       <c r="F32" s="69"/>
       <c r="G32" s="69"/>
-    </row>
-    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="69"/>
+    </row>
+    <row r="33" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>350</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="H33" s="79"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="68" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8388,7 +9047,7 @@
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -8403,7 +9062,7 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -8414,8 +9073,8 @@
       <c r="D4" s="51"/>
       <c r="E4" s="52"/>
       <c r="F4" s="53"/>
-      <c r="G4" s="23" t="s">
-        <v>297</v>
+      <c r="G4" s="83" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -8423,52 +9082,52 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="28" t="s">
+      <c r="F5" s="28" t="s">
         <v>85</v>
       </c>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="28" t="s">
+      <c r="F6" s="28" t="s">
         <v>85</v>
       </c>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E7" t="s">
-        <v>236</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F7" s="28" t="s">
         <v>85</v>
       </c>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="70" t="s">
@@ -8515,36 +9174,36 @@
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D12" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
-      </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" s="28" t="s">
         <v>85</v>
       </c>
+      <c r="G12" s="23"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E13" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="28" t="s">
+      <c r="F13" s="28" t="s">
         <v>85</v>
       </c>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="70" t="s">
@@ -8581,108 +9240,108 @@
         <v>11</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="26" t="s">
-        <v>166</v>
-      </c>
+      <c r="F17" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G17" s="23"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D18" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="26" t="s">
-        <v>166</v>
-      </c>
+      <c r="F18" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="23"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D19" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E19" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="26" t="s">
-        <v>166</v>
-      </c>
+      <c r="F19" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="23"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D20" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
-      </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="26" t="s">
-        <v>166</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G20" s="23"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D21" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
-      </c>
-      <c r="F21" s="41"/>
-      <c r="G21" s="26" t="s">
-        <v>166</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E22" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="46"/>
-      <c r="G22" s="26" t="s">
-        <v>166</v>
-      </c>
+      <c r="F22" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="70" t="s">
@@ -8699,18 +9358,18 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D24" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E24" t="s">
         <v>77</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="26" t="s">
-        <v>166</v>
-      </c>
+      <c r="F24" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="70" t="s">
@@ -8757,18 +9416,18 @@
         <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D29" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E29" t="s">
         <v>94</v>
       </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="27" t="s">
+      <c r="F29" s="27" t="s">
         <v>123</v>
       </c>
+      <c r="G29" s="23"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="70" t="s">
@@ -8802,23 +9461,23 @@
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="62" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="81" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8835,13 +9494,13 @@
     <col min="4" max="4" width="34.140625" customWidth="1"/>
     <col min="5" max="5" width="31.5703125" customWidth="1"/>
     <col min="6" max="6" width="30.5703125" customWidth="1"/>
-    <col min="7" max="7" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
@@ -8856,18 +9515,18 @@
         <v>83</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>308</v>
+      <c r="C4" s="80" t="s">
+        <v>306</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>103</v>
@@ -8875,20 +9534,22 @@
       <c r="F4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="61" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>85</v>
@@ -8900,13 +9561,13 @@
         <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
         <v>133</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>85</v>
@@ -8918,13 +9579,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="28" t="s">
         <v>85</v>
@@ -8989,7 +9650,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
@@ -9033,109 +9694,121 @@
       <c r="B17" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="32" t="s">
-        <v>310</v>
+      <c r="C17" s="81" t="s">
+        <v>308</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G17" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G17" s="61" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>311</v>
+      <c r="C18" s="80" t="s">
+        <v>309</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
         <v>80</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G18" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>312</v>
+      <c r="C19" s="80" t="s">
+        <v>310</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
         <v>97</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>313</v>
+      <c r="C20" s="80" t="s">
+        <v>311</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G20" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>314</v>
+      <c r="C21" s="80" t="s">
+        <v>312</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G21" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>315</v>
+      <c r="C22" s="82" t="s">
+        <v>313</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E22" s="37" t="s">
         <v>89</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G22" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="70" t="s">
@@ -9151,19 +9824,21 @@
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>316</v>
+      <c r="C24" s="80" t="s">
+        <v>314</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G24" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G24" s="61" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="70" t="s">
@@ -9189,37 +9864,41 @@
       <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>317</v>
+      <c r="C27" s="80" t="s">
+        <v>315</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>39</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>318</v>
+      <c r="C28" s="80" t="s">
+        <v>316</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
         <v>77</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="G28" s="61" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="70" t="s">
@@ -9239,7 +9918,9 @@
       <c r="D30" s="51"/>
       <c r="E30" s="52"/>
       <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
+      <c r="G30" s="77" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="70" t="s">
@@ -9249,7 +9930,9 @@
       <c r="D31" s="51"/>
       <c r="E31" s="52"/>
       <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
+      <c r="G31" s="78" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="65" t="s">
@@ -9259,29 +9942,31 @@
       <c r="D32" s="67"/>
       <c r="E32" s="68"/>
       <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
+      <c r="G32" s="78" t="s">
+        <v>374</v>
+      </c>
     </row>
     <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="75" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F33" s="75"/>
       <c r="G33" s="76" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="61" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="5" scale="73" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797A48E8-599E-4C5B-BACF-4D8EEE0BE0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC44011C-9519-40EA-9257-19D22C58596B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="960" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="411">
   <si>
     <t>location</t>
   </si>
@@ -1413,7 +1413,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Coordinates H -&gt; </t>
+      <t xml:space="preserve">K (mg/L) -&gt; </t>
     </r>
     <r>
       <rPr>
@@ -1424,7 +1424,288 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Coordinates_H</t>
+      <t>K_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fe (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fe_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mn (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mn_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Na (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Na_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mg (mg/L) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mg_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ca (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ca_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cl (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cl_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SO4 (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SO4_mg-l</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HCO3 (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HCO3_mg-l</t>
+    </r>
+  </si>
+  <si>
+    <t>Geothermal province -&gt; Geothermal_province</t>
+  </si>
+  <si>
+    <t>Nein, da HCO3 einwertig ist gilt meq/L = mmol/L</t>
+  </si>
+  <si>
+    <r>
+      <t>CLA flow path -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CLA_flow_path</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bore/Spring -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bore_Spring</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mg (mg/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mg_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ca (mg/L) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ca_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SO4 (mg/L) -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SO4_mg-L</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alkalinity (meq/L) -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alkalinity_meq-L</t>
+    </r>
+  </si>
+  <si>
+    <t>liegt in ppb vor, müsste in ppm vorliegen, Faktor / 1.000</t>
+  </si>
+  <si>
+    <r>
+      <t>Well or Spring Name -&gt; Well_or_</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Spring_Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Final depth -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Final_depth</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Rock type -&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Rock_type</t>
     </r>
   </si>
   <si>
@@ -1442,10 +1723,20 @@
       </rPr>
       <t>Coordinates_R</t>
     </r>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">K (mg/L) -&gt; </t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [Daten wurden manuell schon in Excel konvertiert]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Coordinates H -&gt; </t>
     </r>
     <r>
       <rPr>
@@ -1456,241 +1747,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>K_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fe (mg/L) -&gt; </t>
+      <t>Coordinates_H</t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Fe_mg-L</t>
+      <t xml:space="preserve"> [Daten wurden manuell schon in Excel konvertiert]</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mn (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mn_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Na (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Na_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Mg (mg/L) -&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Mg_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ca (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ca_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cl (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cl_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SO4 (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SO4_mg-l</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">HCO3 (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>HCO3_mg-l</t>
-    </r>
-  </si>
-  <si>
-    <t>Geothermal province -&gt; Geothermal_province</t>
-  </si>
-  <si>
-    <t>Nein, da HCO3 einwertig ist gilt meq/L = mmol/L</t>
-  </si>
-  <si>
-    <r>
-      <t>CLA flow path -&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CLA_flow_path</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bore/Spring -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bore_Spring</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mg (mg/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mg_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ca (mg/L) -&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Ca_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SO4 (mg/L) -&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> SO4_mg-L</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Alkalinity (meq/L) -&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Alkalinity_meq-L</t>
-    </r>
-  </si>
-  <si>
-    <t>liegt in ppb vor, müsste in ppm vorliegen, Faktor / 1.000</t>
   </si>
 </sst>
 </file>
@@ -2971,7 +3039,7 @@
         <v>85</v>
       </c>
       <c r="G4" s="61" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2991,7 +3059,7 @@
         <v>85</v>
       </c>
       <c r="G5" s="61" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -3137,7 +3205,7 @@
         <v>165</v>
       </c>
       <c r="G17" s="61" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -3157,7 +3225,7 @@
         <v>165</v>
       </c>
       <c r="G18" s="61" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -3177,7 +3245,7 @@
         <v>165</v>
       </c>
       <c r="G19" s="61" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -3197,7 +3265,7 @@
         <v>165</v>
       </c>
       <c r="G20" s="61" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -3217,7 +3285,7 @@
         <v>165</v>
       </c>
       <c r="G21" s="61" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -3234,10 +3302,10 @@
         <v>80</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G22" s="61" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3267,7 +3335,7 @@
         <v>165</v>
       </c>
       <c r="G24" s="61" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -5184,7 +5252,7 @@
         <v>165</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -8367,7 +8435,7 @@
     <col min="5" max="5" width="29.5703125" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" customWidth="1"/>
     <col min="7" max="7" width="27.140625" customWidth="1"/>
-    <col min="8" max="8" width="63.42578125" customWidth="1"/>
+    <col min="8" max="8" width="76.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -8419,7 +8487,7 @@
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="80" t="s">
         <v>220</v>
       </c>
       <c r="D5" t="s">
@@ -8434,7 +8502,9 @@
       <c r="G5" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="H5" s="23"/>
+      <c r="H5" s="61" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
@@ -8456,7 +8526,7 @@
         <v>234</v>
       </c>
       <c r="H6" s="61" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
@@ -8479,14 +8549,14 @@
         <v>234</v>
       </c>
       <c r="H7" s="61" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="80" t="s">
         <v>227</v>
       </c>
       <c r="D8" t="s">
@@ -8501,13 +8571,15 @@
       <c r="G8" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="H8" s="23"/>
+      <c r="H8" s="61" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="80" t="s">
         <v>228</v>
       </c>
       <c r="D9" t="s">
@@ -8522,7 +8594,9 @@
       <c r="G9" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="61" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
@@ -9024,7 +9098,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" scale="68" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9535,7 +9609,7 @@
         <v>85</v>
       </c>
       <c r="G4" s="61" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -9707,7 +9781,7 @@
         <v>165</v>
       </c>
       <c r="G17" s="61" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -9727,7 +9801,7 @@
         <v>165</v>
       </c>
       <c r="G18" s="61" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -9747,7 +9821,7 @@
         <v>165</v>
       </c>
       <c r="G19" s="61" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -9767,7 +9841,7 @@
         <v>165</v>
       </c>
       <c r="G20" s="61" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
@@ -9787,7 +9861,7 @@
         <v>165</v>
       </c>
       <c r="G21" s="61" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -9807,7 +9881,7 @@
         <v>165</v>
       </c>
       <c r="G22" s="61" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -9837,7 +9911,7 @@
         <v>165</v>
       </c>
       <c r="G24" s="61" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
@@ -9877,7 +9951,7 @@
         <v>165</v>
       </c>
       <c r="G27" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -9897,7 +9971,7 @@
         <v>165</v>
       </c>
       <c r="G28" s="61" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/Anpassung auf globales Datenschema.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucca\OneDrive\SPEICHER\Hochschule\7. Semester\Abschlussarbeit Bearbeitung\Jupyter Notebooks\1_Data-Acquisition-Wrapper\globales_Datenschema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a36cc37384f3e2/SPEICHER/Hochschule/7. Semester/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1_Data-Acquisition-Wrapper/globales_Datenschema/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC44011C-9519-40EA-9257-19D22C58596B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
